--- a/data/attendance/AMPHI_حموي_1_ثانوي.xlsx
+++ b/data/attendance/AMPHI_حموي_1_ثانوي.xlsx
@@ -31,7 +31,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
   <si>
-    <t>حموي 1 ثانوي  |  AMPHI  |  1AS  |  عبد السلام حموي</t>
+    <t>حموي 1 ثانوي  |  AMPHI  |  1AS  |  حموي عبد السلام</t>
   </si>
   <si>
     <t>class_id=8</t>

--- a/data/attendance/AMPHI_حموي_1_ثانوي.xlsx
+++ b/data/attendance/AMPHI_حموي_1_ثانوي.xlsx
@@ -20,7 +20,14 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <t>student_id:a34881a6-554a-4624-9ae0-447737ddb951</t>
+          <t>student_id:5a0d8f4b-8d75-461a-ab32-f5e92ee50360</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0">
+      <text>
+        <r>
+          <t>student_id:54f4388c-8185-4058-9aa0-9f9ba272e60d</t>
         </r>
       </text>
     </comment>
@@ -29,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>حموي 1 ثانوي  |  AMPHI  |  1AS  |  حموي عبد السلام</t>
   </si>
@@ -52,13 +59,16 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
-    <t>08/09/2026</t>
+    <t>02/10/2026</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
     <t>بوكلوة ميار</t>
+  </si>
+  <si>
+    <t>بوناح سمر ميلينا</t>
   </si>
   <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
@@ -139,7 +149,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -176,6 +186,11 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F5FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -204,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -228,6 +243,9 @@
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -570,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -695,7 +713,7 @@
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>550</v>
+        <v>389</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>9</v>
@@ -734,6 +752,50 @@
         <v>0</v>
       </c>
       <c r="N5" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>390</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="9">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9">
+        <v>0</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9">
+        <v>0</v>
+      </c>
+      <c r="I6" s="9">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
+        <v>0</v>
+      </c>
+      <c r="L6" s="9">
+        <v>0</v>
+      </c>
+      <c r="M6" s="9">
+        <v>0</v>
+      </c>
+      <c r="N6" s="9">
         <v>0</v>
       </c>
     </row>
@@ -760,8 +822,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>10</v>
+      <c r="A1" s="10" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -771,12 +833,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -786,27 +848,27 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -816,12 +878,12 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -831,7 +893,7 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/data/attendance/AMPHI_حموي_1_ثانوي.xlsx
+++ b/data/attendance/AMPHI_حموي_1_ثانوي.xlsx
@@ -31,12 +31,131 @@
         </r>
       </text>
     </comment>
+    <comment ref="B7" authorId="0">
+      <text>
+        <r>
+          <t>student_id:8db0277b-0947-4975-b648-c93aa4b0015b</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0">
+      <text>
+        <r>
+          <t>student_id:e43425eb-d158-46c3-985d-8d7fc31214e6</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="0">
+      <text>
+        <r>
+          <t>student_id:a0d37926-540f-4a05-bf21-c90dd19cdc5d</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0">
+      <text>
+        <r>
+          <t>student_id:4e679f82-d2d3-49ce-a598-0728b515ccd8</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="0">
+      <text>
+        <r>
+          <t>student_id:da2e2666-3778-45c0-97d9-1b6097b05ea5</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0">
+      <text>
+        <r>
+          <t>student_id:de7d24b6-cb24-43d4-a8a0-bb3ed23947f8</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0">
+      <text>
+        <r>
+          <t>student_id:a6a23725-9a31-4057-8af0-0e0467c652fe</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0">
+      <text>
+        <r>
+          <t>student_id:fa95329a-d1e1-417d-bb13-5d6f1273a684</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B15" authorId="0">
+      <text>
+        <r>
+          <t>student_id:b00a3738-d937-4051-9692-344debf7f7d8</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0">
+      <text>
+        <r>
+          <t>student_id:f6f36b3d-c45e-4ec4-9c98-b5b7ccd4b62d</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B17" authorId="0">
+      <text>
+        <r>
+          <t>student_id:086497f8-7d61-48a9-ae9a-834d958435bb</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B18" authorId="0">
+      <text>
+        <r>
+          <t>student_id:c78d6e45-15c9-4f38-8d7c-51f22ef33945</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B19" authorId="0">
+      <text>
+        <r>
+          <t>student_id:e84f83f4-4cc4-4058-96cb-ea29640aa266</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0">
+      <text>
+        <r>
+          <t>student_id:cfe51b37-3347-4cae-bcff-347d588210c8</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B21" authorId="0">
+      <text>
+        <r>
+          <t>student_id:9d42909e-4fe1-41b0-a213-c46e47c81220</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B22" authorId="0">
+      <text>
+        <r>
+          <t>student_id:5e929a94-081b-46bc-b566-92aa1e99ae24</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B23" authorId="0">
+      <text>
+        <r>
+          <t>student_id:270fa874-7125-4e91-98ab-e0236677991e</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>حموي 1 ثانوي  |  AMPHI  |  1AS  |  حموي عبد السلام</t>
   </si>
@@ -50,6 +169,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -71,6 +193,57 @@
     <t>بوناح سمر ميلينا</t>
   </si>
   <si>
+    <t>بن عاشور كنزي</t>
+  </si>
+  <si>
+    <t>مباركي هند</t>
+  </si>
+  <si>
+    <t>بوريو امير</t>
+  </si>
+  <si>
+    <t>عميار  بلقيس</t>
+  </si>
+  <si>
+    <t>العزوزي محمد وسيم</t>
+  </si>
+  <si>
+    <t>خلف الله  محمد امين</t>
+  </si>
+  <si>
+    <t>شراك دارين</t>
+  </si>
+  <si>
+    <t>قهواجي مصعب</t>
+  </si>
+  <si>
+    <t>لكحل احمد</t>
+  </si>
+  <si>
+    <t>رغيوة  محمد</t>
+  </si>
+  <si>
+    <t>ناصري رؤى رنيم</t>
+  </si>
+  <si>
+    <t>قيسمنة ياسين</t>
+  </si>
+  <si>
+    <t>عزيون جواد</t>
+  </si>
+  <si>
+    <t>سعدي محمد معتز</t>
+  </si>
+  <si>
+    <t>بوشاقورة احمد شاهين</t>
+  </si>
+  <si>
+    <t>مقلاتي العكي محمد قصي</t>
+  </si>
+  <si>
+    <t>شكيرد محمد فادي</t>
+  </si>
+  <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
   </si>
   <si>
@@ -98,7 +271,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -588,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -614,7 +790,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -624,10 +800,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -669,46 +848,46 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -716,7 +895,7 @@
         <v>389</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="8">
         <v>0</v>
@@ -760,7 +939,7 @@
         <v>390</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="9">
         <v>0</v>
@@ -796,6 +975,754 @@
         <v>0</v>
       </c>
       <c r="N6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>838</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8">
+        <v>0</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8">
+        <v>0</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
+      <c r="N7" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>839</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+      <c r="E8" s="9">
+        <v>0</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="9">
+        <v>0</v>
+      </c>
+      <c r="M8" s="9">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>840</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8">
+        <v>0</v>
+      </c>
+      <c r="L9" s="8">
+        <v>0</v>
+      </c>
+      <c r="M9" s="8">
+        <v>0</v>
+      </c>
+      <c r="N9" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>841</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>842</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="8">
+        <v>0</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8">
+        <v>0</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>843</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>844</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8">
+        <v>0</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>845</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>846</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>847</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>848</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>849</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0</v>
+      </c>
+      <c r="I18" s="9">
+        <v>0</v>
+      </c>
+      <c r="J18" s="9">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9">
+        <v>0</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>850</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+      <c r="N19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>851</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9">
+        <v>0</v>
+      </c>
+      <c r="G20" s="9">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9">
+        <v>0</v>
+      </c>
+      <c r="L20" s="9">
+        <v>0</v>
+      </c>
+      <c r="M20" s="9">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>853</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0</v>
+      </c>
+      <c r="I21" s="8">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8">
+        <v>0</v>
+      </c>
+      <c r="L21" s="8">
+        <v>0</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0</v>
+      </c>
+      <c r="N21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>930</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="9">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9">
+        <v>0</v>
+      </c>
+      <c r="I22" s="9">
+        <v>0</v>
+      </c>
+      <c r="J22" s="9">
+        <v>0</v>
+      </c>
+      <c r="K22" s="9">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9">
+        <v>0</v>
+      </c>
+      <c r="M22" s="9">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>981</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="8">
+        <v>0</v>
+      </c>
+      <c r="D23" s="8">
+        <v>0</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0</v>
+      </c>
+      <c r="F23" s="8">
+        <v>0</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8">
+        <v>0</v>
+      </c>
+      <c r="I23" s="8">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8">
+        <v>0</v>
+      </c>
+      <c r="K23" s="8">
+        <v>0</v>
+      </c>
+      <c r="L23" s="8">
+        <v>0</v>
+      </c>
+      <c r="M23" s="8">
+        <v>0</v>
+      </c>
+      <c r="N23" s="8">
         <v>0</v>
       </c>
     </row>
@@ -815,7 +1742,7 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
@@ -823,77 +1750,82 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
